--- a/Results_experiment/exp_2/reg_summary_12.xlsx
+++ b/Results_experiment/exp_2/reg_summary_12.xlsx
@@ -447,13 +447,13 @@
         <v>530</v>
       </c>
       <c r="D2">
-        <v>0.1464640674809611</v>
+        <v>0.5201351952413044</v>
       </c>
       <c r="E2">
-        <v>12.06481023568111</v>
+        <v>9.046259464399396</v>
       </c>
       <c r="F2">
-        <v>9.528572746099167</v>
+        <v>7.195148908318776</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>509</v>
       </c>
       <c r="D3">
-        <v>-0.129402460775345</v>
+        <v>0.5687215563054804</v>
       </c>
       <c r="E3">
-        <v>7.86598521064144</v>
+        <v>4.860798705435585</v>
       </c>
       <c r="F3">
-        <v>5.019893080362051</v>
+        <v>3.394471868711628</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>0.07127989041271099</v>
+        <v>0.2044883802240047</v>
       </c>
       <c r="E4">
-        <v>8.880841915682215</v>
+        <v>8.219302768316707</v>
       </c>
       <c r="F4">
-        <v>6.615172808386368</v>
+        <v>6.285827597277565</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>371</v>
       </c>
       <c r="D5">
-        <v>0.1378997244266668</v>
+        <v>0.5778613818936162</v>
       </c>
       <c r="E5">
-        <v>6.106945689398895</v>
+        <v>4.273391755678812</v>
       </c>
       <c r="F5">
-        <v>3.733634020380094</v>
+        <v>2.584358854495451</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>325</v>
       </c>
       <c r="D6">
-        <v>-0.1301603080290974</v>
+        <v>-0.1710339064451534</v>
       </c>
       <c r="E6">
-        <v>7.967568666260417</v>
+        <v>8.110367334629268</v>
       </c>
       <c r="F6">
-        <v>5.999514268567929</v>
+        <v>5.989744926484732</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>235</v>
       </c>
       <c r="D7">
-        <v>-0.3737328294497191</v>
+        <v>-4.28355955799867</v>
       </c>
       <c r="E7">
-        <v>6.242098461185774</v>
+        <v>12.24172952956623</v>
       </c>
       <c r="F7">
-        <v>3.825144804823906</v>
+        <v>9.773584876383874</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>0.1785521497648033</v>
+        <v>0.5039010081209556</v>
       </c>
       <c r="E8">
-        <v>6.104240776684259</v>
+        <v>4.743794084889585</v>
       </c>
       <c r="F8">
-        <v>4.104563021005002</v>
+        <v>3.598633162510235</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>0.3093979529920969</v>
+        <v>0.7615618589454763</v>
       </c>
       <c r="E9">
-        <v>11.20398102110219</v>
+        <v>6.583340188374551</v>
       </c>
       <c r="F9">
-        <v>8.722095566402588</v>
+        <v>4.263126824583326</v>
       </c>
     </row>
   </sheetData>
